--- a/samples/Trial_Balance_VS_Jul-26.xlsx
+++ b/samples/Trial_Balance_VS_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>63256.53</v>
+        <v>6408.29</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>165.71</v>
+        <v>160.61</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>55999.94</v>
+        <v>54279.71</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>3743.95</v>
+        <v>3628.93</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>2941.22</v>
+        <v>2850.87</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>6885.51</v>
+        <v>6674</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>16200</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>29022.18</v>
+        <v>28130.66</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D15">
-        <v>-10731.89</v>
+        <v>-10402.22</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D16">
-        <v>1802.68</v>
+        <v>1747.31</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D17">
-        <v>-16494.12</v>
+        <v>-15987.45</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-8457.75</v>
+        <v>-8197.95</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-4067.56</v>
+        <v>-3942.61</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-3266.77</v>
+        <v>-3166.42</v>
       </c>
     </row>
     <row r="21">
@@ -646,7 +646,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D21">
-        <v>-7290</v>
+        <v>-6967.35</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-71229.38</v>
+        <v>-40000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-38026.8</v>
+        <v>-8000</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Equity</v>
       </c>
       <c r="D24">
-        <v>-19533.76</v>
+        <v>-19519.29</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-143550.41</v>
+        <v>-114755.26</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-903.14</v>
+        <v>-721.98</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>52036.14</v>
+        <v>41598.08</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>44835.24</v>
+        <v>35841.62</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>4170.47</v>
+        <v>3333.9</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>5888.3</v>
+        <v>4707.14</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>4583.25</v>
+        <v>3663.89</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>7527.78</v>
+        <v>6017.76</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>2514.27</v>
+        <v>2009.92</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>16470</v>
+        <v>13004.38</v>
       </c>
     </row>
     <row r="35">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>5508.41</v>
+        <v>4403.46</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_VS_Jul-26.xlsx
+++ b/samples/Trial_Balance_VS_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>6408.29</v>
+        <v>29911.2</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>13200</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="14">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-40000</v>
+        <v>-70000</v>
       </c>
     </row>
     <row r="23">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-114755.26</v>
+        <v>-49027.27</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-721.98</v>
+        <v>-227.99</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>41598.08</v>
+        <v>12456.69</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>35841.62</v>
+        <v>10763.84</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>3333.9</v>
+        <v>1000.18</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>4707.14</v>
+        <v>1412.14</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>3663.89</v>
+        <v>1087.83</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>6017.76</v>
+        <v>1816.68</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>2009.92</v>
+        <v>591.6</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>13004.38</v>
+        <v>15605.26</v>
       </c>
     </row>
     <row r="35">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>4403.46</v>
+        <v>1321.04</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_VS_Jul-26.xlsx
+++ b/samples/Trial_Balance_VS_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>29911.2</v>
+        <v>15287.76</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-49027.27</v>
+        <v>-34403.83</v>
       </c>
     </row>
     <row r="26">
